--- a/marketing_report/outputs/Posgrados/Analisis_No_Matcheados/datos_analisis_no_matcheados.xlsx
+++ b/marketing_report/outputs/Posgrados/Analisis_No_Matcheados/datos_analisis_no_matcheados.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
   <si>
     <t>Rango</t>
   </si>
@@ -197,6 +197,9 @@
   </si>
   <si>
     <t>outlook.com</t>
+  </si>
+  <si>
+    <t>outlook.com.ar</t>
   </si>
   <si>
     <t>ucasal.edu.ar</t>
@@ -588,13 +591,13 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C2">
-        <v>82.7</v>
+        <v>80.5</v>
       </c>
       <c r="D2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="E2">
         <v>100</v>
@@ -605,10 +608,10 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C3">
-        <v>16</v>
+        <v>18.3</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -625,7 +628,7 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -925,7 +928,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -959,7 +962,7 @@
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -967,16 +970,16 @@
         <v>54</v>
       </c>
       <c r="B3">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="C3">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="D3">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E3">
-        <v>105.49</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1001,16 +1004,16 @@
         <v>56</v>
       </c>
       <c r="B5">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C5">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D5">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E5">
-        <v>94.12</v>
+        <v>81.81999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1018,16 +1021,16 @@
         <v>57</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6">
-        <v>50</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1052,16 +1055,16 @@
         <v>59</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8">
-        <v>50</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1069,16 +1072,16 @@
         <v>60</v>
       </c>
       <c r="B9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>75</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1086,15 +1089,32 @@
         <v>61</v>
       </c>
       <c r="B10">
+        <v>4</v>
+      </c>
+      <c r="C10">
         <v>3</v>
-      </c>
-      <c r="C10">
-        <v>2</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
       <c r="E10">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11">
+        <v>3</v>
+      </c>
+      <c r="C11">
+        <v>2</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
         <v>66.67</v>
       </c>
     </row>

--- a/marketing_report/outputs/Posgrados/Analisis_No_Matcheados/datos_analisis_no_matcheados.xlsx
+++ b/marketing_report/outputs/Posgrados/Analisis_No_Matcheados/datos_analisis_no_matcheados.xlsx
@@ -8,16 +8,14 @@
   </bookViews>
   <sheets>
     <sheet name="Distribucion_Consultas" sheetId="1" r:id="rId1"/>
-    <sheet name="Tiempos_Resolucion" sheetId="2" r:id="rId2"/>
-    <sheet name="Deciles_Tiempos" sheetId="3" r:id="rId3"/>
-    <sheet name="Dominios" sheetId="4" r:id="rId4"/>
+    <sheet name="Dominios" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>Rango</t>
   </si>
@@ -67,102 +65,6 @@
     <t>10+ consultas</t>
   </si>
   <si>
-    <t>Metrica</t>
-  </si>
-  <si>
-    <t>Valor</t>
-  </si>
-  <si>
-    <t>Promedio</t>
-  </si>
-  <si>
-    <t>Mediana</t>
-  </si>
-  <si>
-    <t>Moda</t>
-  </si>
-  <si>
-    <t>Personas Analizadas</t>
-  </si>
-  <si>
-    <t>86 días</t>
-  </si>
-  <si>
-    <t>39 días</t>
-  </si>
-  <si>
-    <t>3 días</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>Decil</t>
-  </si>
-  <si>
-    <t>Dias</t>
-  </si>
-  <si>
-    <t>D10</t>
-  </si>
-  <si>
-    <t>D20</t>
-  </si>
-  <si>
-    <t>D30</t>
-  </si>
-  <si>
-    <t>D40</t>
-  </si>
-  <si>
-    <t>D50 (Mediana)</t>
-  </si>
-  <si>
-    <t>D60</t>
-  </si>
-  <si>
-    <t>D70</t>
-  </si>
-  <si>
-    <t>D80</t>
-  </si>
-  <si>
-    <t>D90</t>
-  </si>
-  <si>
-    <t>D100 (Máx)</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t>46</t>
-  </si>
-  <si>
-    <t>97</t>
-  </si>
-  <si>
-    <t>214</t>
-  </si>
-  <si>
-    <t>225</t>
-  </si>
-  <si>
-    <t>299</t>
-  </si>
-  <si>
     <t>Domain</t>
   </si>
   <si>
@@ -182,9 +84,6 @@
   </si>
   <si>
     <t>gmail.com</t>
-  </si>
-  <si>
-    <t>gmil.com</t>
   </si>
   <si>
     <t>hotmail.com</t>
@@ -591,13 +490,13 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="C2">
-        <v>80.5</v>
+        <v>70.2</v>
       </c>
       <c r="D2">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E2">
         <v>100</v>
@@ -608,10 +507,10 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C3">
-        <v>18.3</v>
+        <v>27.7</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -628,7 +527,7 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -780,177 +679,29 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B6" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" t="s">
-        <v>33</v>
-      </c>
-      <c r="B7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" t="s">
-        <v>36</v>
-      </c>
-      <c r="B10" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" t="s">
-        <v>37</v>
-      </c>
-      <c r="B11" t="s">
-        <v>47</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>52</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -962,159 +713,142 @@
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="B3">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="C3">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="D3">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E3">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E4">
-        <v>100</v>
+        <v>73.33</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="B5">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>81.81999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>33.33</v>
+        <v>200</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
         <v>2</v>
       </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
       <c r="E7">
-        <v>200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="B8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>33.33</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="B9">
+        <v>3</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9">
         <v>1</v>
       </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
       <c r="E9">
-        <v>100</v>
+        <v>66.67</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="B10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
       <c r="E10">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" t="s">
-        <v>62</v>
-      </c>
-      <c r="B11">
-        <v>3</v>
-      </c>
-      <c r="C11">
-        <v>2</v>
-      </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11">
         <v>66.67</v>
       </c>
     </row>
